--- a/doc/OTH-AT_Command_Status.xlsx
+++ b/doc/OTH-AT_Command_Status.xlsx
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OTH-AT 명령 상태 요약 (2026-10-05, OTH_ESP32_C)</t>
+          <t>OTH-AT 명령 상태 요약 (2026-10-06, OTH_ESP32_C)</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -562,7 +562,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>검증 환경: COM7 보드(ESP32-C3), AP kangaps25, broker.emqx.io, AWS IoT 테스트 계정(ap-southeast-2).</t>
+          <t>검증 환경: COM7 보드(ESP32-C3), AP kangaps25, broker.emqx.io, AWS IoT 테스트 계정(ap-southeast-2). AWS 볼륨(2026-10-06): PC 모의 인증서버 + broker.emqx.io(엔드포인트 대용) + PC MQTT 클라이언트(클라우드 역할).</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>0,1,2,6 값. 3-5,7,10,11 null</t>
+          <t>0 엔드포인트, 1 포트, 2 클라이언트ID(MAC, 인증 후 MAC_토큰), 3 인증서버, 4/5 RootCA URL, 6 지역, 7 토큰, 10 MCU 버전, 11 MCU 체크섬. 미설정 null</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>&lt;thing&gt;/up/&lt;apiNo&gt;, QoS1. A100은 연결 절차 재시작</t>
+          <t>header/values 봉투, apiGroup 자동(A1x 001~A14x 004, A5xx 005). A100/A102는 Conn, 그 외 Event 토픽, QoS1. A100은 연결 절차 재시작. 미연결 SEND ERROR 2</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>CONFIG~CONNECT, DISCONNECT, SEND</t>
+          <t>CONFIG~CONNECT OK 0, DISCONNECT ERROR 2, SEND OK, CERTIFICATE ERROR 112 확인. 실패 시 60초 뒤 재시도</t>
         </is>
       </c>
     </row>
@@ -2428,9 +2428,9 @@
           <t>AWS_RECV</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>구현(미검증)</t>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>검증완료</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2440,33 +2440,225 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>&lt;thing&gt;/down/&lt;apiNo&gt;. AWS CLI 세션 만료로 미시험</t>
+          <t>Control 토픽 수신 -&gt; attributes(없으면 values 필드 평탄화). deviceId 불일치 폐기. 모의 클라우드(broker.emqx.io)로 확인, 실서버 미시험</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>AWS_SET (OTH Platform 추가)</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>검증완료</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>cmd_oth_aws.c</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>개발용. 인덱스 0/1/3-7 기록, null=삭제. 인증서버/토큰 변경 시 저장 인증서 폐기, RootCA URL 변경 시 RootCA 폐기</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>MCU_READY (OTH Platform 추가)</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>검증완료</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>cmd_oth_aws.c</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>호스트 MCU 버전 -&gt; AWS_GET 10, A100/A500 V02, 페어링 장치정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>MOTA_START / MOTA_READY / MOTA_DATA / MOTA_DATA_END (OTH Platform 추가)</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>검증완료</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>oth_fota.c</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>MCU 이미지를 비활성 OTA 슬롯에 저장 후 256바이트 블록 중계(바이트 스터핑, 블록/전체 CRC32). 600바이트 이미지 CRC PC 계산값과 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>클라우드 지시 A502 / A511 / A531 / A521 / A001 (모듈 처리)</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>검증완료</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>cmd_oth_aws.c, oth_fota.c</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>A502 -&gt; A500 자동 응답. A511 암호화 FOTA: 해시 불일치 거부(A510 900), 정상 설치·재부팅·versionChangeW true. A521 MCU FOTA -&gt; MOTA_COUNT, 완료 후 versionChangeM true. A001 인증서 갱신 후 재접속</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>페어링 서버 TCP 47000 (모듈 처리)</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>구현(미검증)</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>oth_pairing.c</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>GEN2 프레임 DP0100-0400, AES-128 세션, SoftAP 경유 접속만 허용. 앱(또는 별도 Wi-Fi 단말) 없어 미시험</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>A101 등록 해지 (모듈 처리)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>구현(미검증)</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>cmd_oth_aws.c</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>AWS_RECV 전달 + A102 발행 + 인증서·NV 전체 삭제 + 재부팅. 보드 AP 프로필까지 지워져 시험 보류</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
           <t>COAP</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>COAP_GET / COAP_SET / COAP_MSG</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>미구현</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>범위 제외 결정(2026-10-05)</t>
         </is>
@@ -2630,7 +2822,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>페어링 패키지 = aws_conf.json(endpoint, template, parameters) + aws_claim.pem(클레임 인증서+키)</t>
+          <t>OTH Platform: SoftAP TCP 47000 페어링 서버(DP0100-0400)로 RootCA URL 1/2, 인증서버, MQTT 엔드포인트/포트, 지역, 집 AP 수신 -&gt; 접속 후 SoftAP 종료, AUCONMODE 1 저장</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2834,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Fleet Provisioning by Claim (최초 1회, 장치 인증서·Thing 이름 보관)</t>
+          <t>인증서버 GET /register/token/&lt;MAC&gt; -&gt; 토큰, /register/auth/&lt;MAC&gt;/&lt;토큰&gt; -&gt; 장치 인증서·키(키는 암호화 NVS). 이후 저장값 재사용, A001로 갱신</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2846,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>송신 &lt;thing&gt;/up/&lt;apiNo&gt;, 수신 &lt;thing&gt;/down/&lt;apiNo&gt;</t>
+          <t>&lt;root&gt;/{Conn|Event|Control|Lwt}/&lt;MIB19 그룹&gt;/&lt;MIB18 모델&gt;/&lt;MAC_토큰&gt;, header/values 봉투. root는 Kconfig AT_MODEM_OTH_TOPIC_ROOT(기본 OTHERS)</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2858,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>모듈이 처리하지 않고 호스트로 전달 (페이로드 형식 미정의)</t>
+          <t>모듈이 처리: A502-&gt;A500, A511/A531 모듈 FOTA(평문 또는 AES-256-CBC, SHA-256, 이미지ID), A521 MCU FOTA(MOTA_* 중계). 호스트로는 전달 안 함</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2972,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>AWS_RECV (클라우드-&gt;장치) - AWS CLI 로그인 후 시험</t>
+          <t>AWS 페어링 서버(TCP 47000) 앱 시험, A101 등록 해지, 실제 인증서버/AWS IoT 엔드포인트 접속</t>
         </is>
       </c>
     </row>
@@ -2840,7 +3032,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>AWS_GET 10/11 (MCU_READY 명령, MCU FOTA) 정의 없음</t>
+          <t>AWS_GET 10/11, MCU_READY, MOTA_* - 문서 미정의라 OTH Platform 확장으로 구현(명령체계 코드 OT 레지스트리 등록 필요)</t>
         </is>
       </c>
     </row>

--- a/doc/OTH-AT_Command_Status.xlsx
+++ b/doc/OTH-AT_Command_Status.xlsx
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OTH-AT 명령 상태 요약 (2026-10-06, OTH_ESP32_C)</t>
+          <t>OTH-AT 명령 상태 요약 (2026-10-09, OTH_ESP32_C)</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>mode 1: 부팅·링크 끊김 시 5초 간격 재접속. type 0-3은 저장·보고만</t>
+          <t>mode 1: 링크 끊김·부팅 접속 실패 시 무한 재접속(3초 간격 3회 → ASSOCIATED:2 → 20초 휴식 반복, DISASSOCIATED는 즉시). 같은 AP로의 재접속 명령은 연결 유지. type 0-3은 저장·보고만. 2026-10-09 AP 끔/켬 실기 확인(README Phase 23)</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>persistence 0/1/2, 자동 구독. TLS 옵션 4만(1,2 거부)</t>
+          <t>persistence 0/1/2, 자동 구독. TLS 옵션 4만(1,2 거부) / 2026-10-09: 수신 메시지 8 KB까지 재조립해 MQTT_SUB_RECV 1회로 전달(2000/6000/8192 B 실기 확인), 8 KB 초과는 알림 없이 폐기(문서에 해당 알림 없음)</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2883,6 +2883,42 @@
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>명령 줄 안의 LF는 데이터로 유지 (M2M NET_SEND에도 있던 버그 수정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>부팅 중 명령 보류 (공용, M2M 문서 1.5와 동일)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>초기화 전 모든 줄, 부팅 자동 접속 중 네트워크 명령을 최대 10개/16 KB 보류 후 순서대로 실행(IPALLOCATED, 첫 실패 라운드, 부팅 15초 중 먼저). 초과 시 ERROR 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 재접속</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>링크 끊김·부팅 접속 실패: 3초 간격 3회 → ASSOCIATED:2 → 20초 휴식, 무한 반복. 이미 붙어 있거나 접속 중인 AP로의 ASSOCIATE/SCONN/SMODE 99는 연결을 끊지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>큰 MQTT 수신 메시지</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>8 KB까지 재조립 후 MQTT_SUB_RECV 1회. 초과분은 폐기(OTH-AT 문서에 오류 알림 없음). USB 출력은 1 KB 단위로 나눠 씀(공용)</t>
         </is>
       </c>
     </row>
